--- a/data/trans_orig/IP1005-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP1005-Clase-trans_orig.xlsx
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>197498</t>
+          <t>197515</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>399809</t>
+          <t>399770</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4534</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>101191</t>
+          <t>101046</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>123201</t>
+          <t>123782</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>226876</t>
+          <t>226768</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3420</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>68972</t>
+          <t>69387</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>144152</t>
+          <t>143821</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4684</t>
+          <t>4477</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>4548</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6269</t>
+          <t>6202</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>634172</t>
+          <t>634379</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>680228</t>
+          <t>680055</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1317190</t>
+          <t>1317257</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3843</t>
+          <t>3565</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85159</t>
+          <t>85137</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>174360</t>
+          <t>174638</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2539</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>2729</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>3754</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>90190</t>
+          <t>90223</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>92404</t>
+          <t>93382</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>184917</t>
+          <t>185086</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3827</t>
+          <t>3404</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>83228</t>
+          <t>84116</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>167268</t>
+          <t>167691</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>3492</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3466</t>
+          <t>3482</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>202619</t>
+          <t>202136</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>429026</t>
+          <t>429010</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>442</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5240</t>
+          <t>4786</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4748</t>
+          <t>4738</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7341</t>
+          <t>7381</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>668841</t>
+          <t>669295</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>673638</t>
+          <t>673639</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>708753</t>
+          <t>708763</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1380241</t>
+          <t>1380201</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1386256</t>
+          <t>1386460</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,92%</t>
         </is>
       </c>
     </row>
@@ -6380,47 +6380,47 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5561</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>4,93%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>2098</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>640</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5854</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>5,19%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2098</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5833</t>
+          <t>5516</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -6493,12 +6493,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>106892</t>
+          <t>107185</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>112106</t>
+          <t>112116</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>212627</t>
+          <t>212944</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>217818</t>
+          <t>217820</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>3539</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3383</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -6836,7 +6836,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72005</t>
+          <t>71889</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>133885</t>
+          <t>133470</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>605</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>5552</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>961</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6169</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>217627</t>
+          <t>218025</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>222971</t>
+          <t>222972</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>207853</t>
+          <t>208251</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>428262</t>
+          <t>427575</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>433481</t>
+          <t>433470</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7792,7 +7792,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -7865,7 +7865,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>64701</t>
+          <t>64970</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>125573</t>
+          <t>125827</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8065,7 +8065,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5714</t>
+          <t>5744</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1390</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>7670</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11182</t>
+          <t>10984</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -8173,7 +8173,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>665788</t>
+          <t>665758</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -8188,7 +8188,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>701404</t>
+          <t>702067</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>708347</t>
+          <t>708378</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1370057</t>
+          <t>1370255</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1378197</t>
+          <t>1378165</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">

--- a/data/trans_orig/IP1005-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP1005-Clase-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -835,47 +835,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>104352</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1183,42 +1183,42 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>87389</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1296,52 +1296,52 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>87389</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>87389</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>87389</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1521,47 +1521,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>67392</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,107 +1751,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3218</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3228</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3230</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>302</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>200091</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>197515</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>197505</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,68%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,4%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,39%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>606</t>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>399770</t>
+          <t>399577</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>303</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2099,102 +2099,102 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3142</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>632</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3074</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3176</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,61%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>3,05%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1333</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3507</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>4575</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1333</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4642</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>126589</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>124147</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,53%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>103488</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>101046</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>100944</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,39%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,05%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>96,95%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>126589</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>123782</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>97,24%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>346</t>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>226768</t>
+          <t>226835</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2437,107 +2437,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3216</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>4,44%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>602</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3005</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3292</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>4,15%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>3441</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -2550,72 +2550,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>71790</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>69176</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>99,17%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>95,56%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>71790</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>69387</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>143821</t>
+          <t>143970</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2785,94 +2785,94 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>4133</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
           <t>1274</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>4477</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>4493</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>4548</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2577</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>5911</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>2577</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>6202</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,05%</t>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -2893,102 +2893,102 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1027</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>683300</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>680470</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,81%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>99,4%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>951</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>637582</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>634379</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>634363</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,8%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>99,3%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1027</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>683300</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>680055</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>1320882</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>1317548</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>1322819</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>99,81%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>99,34%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1320882</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1317257</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1322818</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1029</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>953</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1029</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3189,7 +3189,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3357,107 +3357,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3302</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3972</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,75%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>4,49%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3329</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>661</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3565</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -3470,74 +3470,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>87778</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>85137</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>84467</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>88439</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,25%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,27%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,51%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>257</t>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>174638</t>
+          <t>174874</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3583,57 +3583,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3705,102 +3705,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3373</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,51%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>443</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2506</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2699</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,48%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1114</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2729</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4370</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1114</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3754</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -3813,74 +3813,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>95439</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>92738</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,3%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,49%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>92286</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>90223</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>90030</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>92729</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,52%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,3%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,09%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>95439</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>93382</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,3%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,16%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>272</t>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>185086</t>
+          <t>184470</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3926,57 +3926,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4043,92 +4043,92 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3412</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,93%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>679</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2774</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3404</t>
+          <t>3396</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4156,72 +4156,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>86211</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>83478</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,22%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,07%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>84205</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>86211</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>84116</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,22%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>167691</t>
+          <t>167699</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4269,57 +4269,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4386,107 +4386,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>694</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3492</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3911</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4188</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>694</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3482</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -4499,74 +4499,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>297</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>204934</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>202136</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>201717</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,66%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,3%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,1%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>619</t>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>429010</t>
+          <t>428304</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4612,57 +4612,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>298</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4842,47 +4842,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>149169</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -4955,57 +4955,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5185,47 +5185,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>53911</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -5298,57 +5298,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1351</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>4758</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>1797</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>442</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>4786</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5476</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,27%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,07%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>1351</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>4738</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>886</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7381</t>
+          <t>6919</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -5528,74 +5528,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1016</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>712150</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>708743</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,81%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>99,33%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>970</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>672284</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>669295</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>673639</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>668605</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>673638</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,73%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,29%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>99,93%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1016</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>712150</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>708763</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>99,34%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>1986</t>
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1380201</t>
+          <t>1380663</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1386460</t>
+          <t>1386696</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,94%</t>
         </is>
       </c>
     </row>
@@ -5641,57 +5641,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>973</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5824,7 +5824,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6105,47 +6105,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>83090</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -6218,57 +6218,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6335,92 +6335,92 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2098</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5499</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,88%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>2098</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5561</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>4,93%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2098</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>638</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5516</t>
+          <t>5544</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -6448,72 +6448,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>110648</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>107247</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>112109</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,14%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,12%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,43%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>105714</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>110648</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>107185</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>112116</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,14%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>212944</t>
+          <t>212916</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>217820</t>
+          <t>217822</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6561,57 +6561,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6678,107 +6678,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3663</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,86%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>677</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3539</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4291</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>677</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3798</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -6791,72 +6791,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>74751</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>71765</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,1%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,14%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>74751</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>71889</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>133470</t>
+          <t>132977</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -6904,57 +6904,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7021,74 +7021,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3154</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2319</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>605</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5552</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>755</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5537</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,04%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>2,48%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2603</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>5</t>
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>6534</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -7134,72 +7134,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>210305</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>207700</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,74%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,5%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>337</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>221258</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>218025</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>222972</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>218040</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>222822</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,96%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>97,52%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>210305</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>208251</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,74%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,77%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>427575</t>
+          <t>427897</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>433470</t>
+          <t>433390</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -7247,57 +7247,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7477,47 +7477,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>136194</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -7590,57 +7590,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7707,107 +7707,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2979</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>4,39%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>549</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2855</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>2779</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>3085</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -7820,72 +7820,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>67276</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>64846</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>95,61%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>67276</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>64970</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>125827</t>
+          <t>126133</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -7933,57 +7933,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8050,72 +8050,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3872</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1342</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>8256</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>2319</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>605</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5744</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5985</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>3872</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>1359</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>7670</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3074</t>
+          <t>3288</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10984</t>
+          <t>11137</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -8163,74 +8163,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>705865</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>701481</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>708395</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>98,84%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,81%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1009</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>669183</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>665758</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>670897</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>665517</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>670900</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,65%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,14%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>99,91%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1011</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>705865</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>702067</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>708378</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>98,92%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>2020</t>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1370255</t>
+          <t>1370102</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1378165</t>
+          <t>1377951</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -8276,57 +8276,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>1013</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1017</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
